--- a/excel/output_stats_vfvv/ludcmp/EfficiencyStats.xlsx
+++ b/excel/output_stats_vfvv/ludcmp/EfficiencyStats.xlsx
@@ -490,28 +490,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>51.9886</v>
+        <v>51.3903</v>
       </c>
       <c r="D2" t="n">
         <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>42.3863</v>
+        <v>41.6684</v>
       </c>
       <c r="F2" t="n">
-        <v>355.16</v>
+        <v>358.28</v>
       </c>
       <c r="G2" t="n">
-        <v>357.29</v>
+        <v>362.28</v>
       </c>
       <c r="H2" t="n">
-        <v>332.4</v>
+        <v>334.226</v>
       </c>
       <c r="I2" t="n">
-        <v>331.573</v>
+        <v>333.295</v>
       </c>
       <c r="J2" t="n">
-        <v>59637200000</v>
+        <v>88812600000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
